--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-12T18:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T18:21:01+01:00</t>
+    <t>2025-11-13T17:39:30+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,10 +532,10 @@
 </t>
   </si>
   <si>
-    <t>Next Step</t>
-  </si>
-  <si>
-    <t>Next step in the grading process after photography. (4000-series)</t>
+    <t>Grading Pending</t>
+  </si>
+  <si>
+    <t>Next step in grading this examination. (4000-series)</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:forrigeUndersokelse</t>
@@ -548,7 +548,7 @@
 </t>
   </si>
   <si>
-    <t>Next Step Previous Examination</t>
+    <t>Next Examination Previous Examination</t>
   </si>
   <si>
     <t>The next step in the screening process after the previous examination. (3000-series)</t>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-15T17:14:08+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,10 +532,10 @@
 </t>
   </si>
   <si>
-    <t>Next Step</t>
-  </si>
-  <si>
-    <t>Next step in the grading process after photography. (4000-series)</t>
+    <t>Grading Pending</t>
+  </si>
+  <si>
+    <t>Next step in grading this examination. (4000-series)</t>
   </si>
   <si>
     <t>DiagnosticReport.extension:forrigeUndersokelse</t>
@@ -548,7 +548,7 @@
 </t>
   </si>
   <si>
-    <t>Next Step Previous Examination</t>
+    <t>Next Examination Previous Examination</t>
   </si>
   <si>
     <t>The next step in the screening process after the previous examination. (3000-series)</t>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-15T17:14:08+01:00</t>
+    <t>2025-11-16T16:39:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6720,7 +6720,7 @@
         <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>23</v>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.8.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T17:09:32+02:00</t>
+    <t>2026-04-17T16:52:07+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.0</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T16:52:07+02:00</t>
+    <t>2026-05-08T13:22:39+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:22:39+02:00</t>
+    <t>2026-06-05T15:47:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T15:47:27+02:00</t>
+    <t>2026-06-08T15:50:57+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
